--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64977_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64977_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R68dee98e28cf44f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8e15025663624c26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    136.0422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    185.0122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    156.9335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    195.9647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    154.5806</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    156.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    139.3874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    139.9891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64977_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64977_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8e15025663624c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1e74aad9cf8b47b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    155.3317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    193.7110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    128.1777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    153.7241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    175.2596</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    176.8157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    215.8159</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    311.0709</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    152.7595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    153.6186</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    304.5791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    130.1679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    159.0358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    158.9905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    214.9909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    213.2668</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    150.7062</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    167.7431</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    223.4352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    260.7720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    249.0839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    289.7394</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    194.8981</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    174.9374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.5584</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.8295</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.9847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    136.7803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    155.3157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.0835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    149.3636</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    131.4251</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.2698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    106.5207</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.1570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.8143</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    135.2556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    173.8615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    192.7803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    213.1332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    136.6976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
